--- a/services_forms/006_food_online_order_form--services_forms.xlsx
+++ b/services_forms/006_food_online_order_form--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-veggie'}</t>
+          <t>non-veggie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Veggie'}</t>
+          <t>Non-Veggie</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'soft'}</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Soft'}</t>
+          <t>Soft</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hard'}</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hard'}</t>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hot'}</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Hot'}</t>
+          <t>Hot</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cold'}</t>
+          <t>cold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cold'}</t>
+          <t>Cold</t>
         </is>
       </c>
     </row>
